--- a/www/terminologies/ASS-X16-CorrespondanceType-Classe-DMP.xlsx
+++ b/www/terminologies/ASS-X16-CorrespondanceType-Classe-DMP.xlsx
@@ -107,13 +107,13 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>http://loinc.org|3.0.1</t>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A03-ClasseDocument/FHIR/TRE-A03-ClasseDocument|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A03-ClasseDocument/FHIR/TRE-A03-ClasseDocument</t>
   </si>
   <si>
     <t>11369-6</t>
@@ -380,7 +380,7 @@
     <t>101881-1</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire|20240329120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
   </si>
   <si>
     <t>AUTORIS-SOINS</t>
@@ -479,10 +479,10 @@
     <t>PRESC-ORTHOPTIE</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A12-NomenclatureASTM/FHIR/TRE-A12-NomenclatureASTM|20231215120000</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A10-NomenclatureURN/FHIR/TRE-A10-NomenclatureURN|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A12-NomenclatureASTM/FHIR/TRE-A12-NomenclatureASTM</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A10-NomenclatureURN/FHIR/TRE-A10-NomenclatureURN</t>
   </si>
   <si>
     <t>E1762</t>
